--- a/docs/validation/V09_Channel_Baseline_Integrity.xlsx
+++ b/docs/validation/V09_Channel_Baseline_Integrity.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -774,7 +774,7 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n"/>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" ht="29.5" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
         <is>
           <t>When you run it</t>
@@ -782,7 +782,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>When measure folder 05 Channel closes; at the model pass; confirmed again on R1 Page 3 when it is built.</t>
+          <t>When measure folder 05 Channel closes; at the model pass; confirmed again on R1 Page 3 and R2 Page 2 when they are built.</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Power BI Desktop — DAX query view in the model file, then report R1.</t>
+          <t>Power BI Desktop — DAX query view in the model file, then reports R1 and R2.</t>
         </is>
       </c>
       <c r="D13" s="7" t="n"/>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="29" customHeight="1">
+    <row r="47" ht="43" customHeight="1">
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>This query tries every combination of the two fields a reader can pick on the channel pages, and lists only the ones where the baseline is blank.</t>
+          <t>This query tries every combination of beverage class, item type and year, and lists only the ones where the baseline is blank. The year stands in for the date slicer that is synced across every page: a baseline that holds while 2019 is selected but goes blank when the date slicer leaves 2019 out is the most likely failure, and the earlier two-field version of this query could not see it.</t>
         </is>
       </c>
     </row>
@@ -1216,370 +1216,332 @@
     <row r="55" ht="15" customHeight="1">
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SUMMARIZE ( DimItem, DimItem[BeverageClass], DimItem[ItemType] ),</t>
+          <t xml:space="preserve">        CROSSJOIN (</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "2019 baseline", [On-Premise Share 2019 Baseline]</t>
+          <t xml:space="preserve">            CALCULATETABLE ( VALUES ( DimDate[Year] ), FactItemMovement ),</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ),</t>
+          <t xml:space="preserve">            SUMMARIZE ( DimItem, DimItem[BeverageClass], DimItem[ItemType] )</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ISBLANK ( [2019 baseline] )</t>
+          <t xml:space="preserve">        ),</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="B59" s="18" t="inlineStr">
         <is>
+          <t xml:space="preserve">        "2019 baseline", [On-Premise Share 2019 Baseline]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ISBLANK ( [2019 baseline] )</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="18" t="inlineStr">
+        <is>
           <t>)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="29" customHeight="1">
-      <c r="A61" s="16" t="n">
+    <row r="63" ht="6" customHeight="1"/>
+    <row r="64" ht="29" customHeight="1">
+      <c r="A64" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Read the grid. Each row is a combination that would make the baseline card go blank. An empty grid means every combination has a value.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="B62" s="17" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Why this query is written this way.  A simpler query style (SUMMARIZECOLUMNS) silently drops rows whose values are all blank — which would hide exactly the rows this check looks for. ADDCOLUMNS over SUMMARIZE keeps them.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="46" customHeight="1">
-      <c r="B63" s="17" t="inlineStr">
+    <row r="66" ht="46" customHeight="1">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>When you have written the result down.  Close the query tab with the × on its tab. Queries left open in DAX query view are kept with the file, and the model file should hold nothing but the model. Then close Power BI Desktop without saving, unless you changed something on purpose.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="B64" s="13" t="inlineStr">
+    <row r="67" ht="20" customHeight="1">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>4.3 Open the R1 report file</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>Open File Explorer and go to X:\retail-sector-health\pbip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Double-click the R1 file — R1_Retail_Sector_Health.pbip. Power BI Desktop opens it and shows the first report page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>The page tabs run along the bottom of the window: Page 1, Page 2 and so on. Select a tab to move to that page.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Open File Explorer and go to X:\retail-sector-health\pbip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Double-click the R1 file — R1_Retail_Sector_Health.pbip. Power BI Desktop opens it and shows the first report page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>The page tabs run along the bottom of the window: Page 1, Page 2 and so on. Select a tab to move to that page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>To inspect one visual, click it once. A thin frame appears around it. Then look at the Visualizations pane on the right:</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="29" customHeight="1">
-      <c r="B69" s="19" t="inlineStr">
+    <row r="72" ht="29" customHeight="1">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C69" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>The Build visual icon (the first icon, a small chart) shows the wells — X-axis, Y-axis, Column y-axis, Line y-axis, Legend, Values — and exactly which field or measure sits in each.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="29" customHeight="1">
-      <c r="B70" s="19" t="inlineStr">
+    <row r="73" ht="29" customHeight="1">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>The Format visual icon (the paintbrush) shows the formatting, including the Y-axis and Secondary y-axis sections.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="29" customHeight="1">
-      <c r="B71" s="19" t="inlineStr">
+    <row r="74" ht="29" customHeight="1">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>The Filters pane, to the left of the Visualizations pane, shows the filters on this visual, on this page and on all pages. Select the arrow at its edge to open it if it is collapsed.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="B72" s="13" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>4.4 Part 2 — confirm it on the page (once R1 Page 3 exists)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>Go to Page 3 of R1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>Find visual 3.2, the On-Premise Share card, and visual 3.10, the on-premise share versus 2019 line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>Click each value in the page’s slicers in turn — each beverage class, each item type — and watch the two visuals.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Go to Page 3 of R1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Find visual 3.2, the On-Premise Share card, and visual 3.10, the on-premise share versus 2019 line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="43" customHeight="1">
+      <c r="A78" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Step through the date slicer — include at least one range that leaves 2019 out — and click each bar in 3.6, Volume Gap by Class, which filters the page by beverage class. Watch the two visuals. R1 Page 3 has no beverage-class or item-type slicer of its own (document 15 §5.3); those slicers are on R2 Page 2, covered in Part 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>Note any selection that makes 3.2 show (Blank) or makes the 3.10 line disappear.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="8" customHeight="1"/>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>5. DECIDE: PASS OR FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>If you see</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>It means</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>Part 1 returns no rows and no selection blanks the visuals in Part 2</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>The baseline holds for every choice a reader can make</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="42" customHeight="1">
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Part 1 lists combinations, or a selection blanks a visual</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Those selections have no 2019 history</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>Fail — list them</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>Remember.  Part 2 is only possible once report R1 is built. At the model pass, record Part 1; at the report pass, update the same row with Part 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="8" customHeight="1"/>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>6. RECORD THE RESULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>6.1 In document 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="16" t="n">
+    <row r="80" ht="16" customHeight="1">
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>4.5 Part 3 — R2 Page 2, the item-type baseline (once R2 Page 2 exists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="29.5" customHeight="1">
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>R2 Page 2 compares each item type’s share with 2019 in visuals 5.3, 5.6 and 5.8. They use a different measure, Item Type Share vs 2019 (pp), so Part 1 does not test them. Run this in DAX query view in the model file, the same way as Part 1:</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>EVALUATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>FILTER (</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADDCOLUMNS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CROSSJOIN (</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            CALCULATETABLE ( VALUES ( DimDate[Year] ), FactItemMovement ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            SUMMARIZE ( DimItem, DimItem[BeverageClass], DimItem[ItemType] )</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "Share vs 2019", [Item Type Share vs 2019 (pp)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ISBLANK ( [Share vs 2019] )</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="29.5" customHeight="1">
+      <c r="A93" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="16" t="n">
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>Read the grid. Each row is a class, type and year where the comparison with 2019 goes blank. A type that moved no cases at all in that year is expected to be blank — note it as explained. Any other row is a failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>Select the Run Summary tab. Find the row for this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="29" customHeight="1">
-      <c r="B89" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr">
-        <is>
-          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="29" customHeight="1">
-      <c r="B90" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr">
-        <is>
-          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="29" customHeight="1">
-      <c r="B91" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="B92" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="inlineStr">
-        <is>
-          <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="B93" s="18" t="inlineStr">
-        <is>
-          <t>git -C X:\retail-sector-health log -1 --format=%h</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="6" customHeight="1"/>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>Open R2_Consumer_Stress.pbip from X:\retail-sector-health\pbip and go to Page 2. Set the date slicer to a range that leaves 2019 out.</t>
+        </is>
+      </c>
+    </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 9.</t>
+          <t>Click each value in the ItemType and BeverageClass slicers (5.1) in turn and watch visuals 5.3, 5.6 and 5.8.</t>
         </is>
       </c>
     </row>
@@ -1589,124 +1551,101 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Fill in four cells on that row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C97" s="14" t="inlineStr">
-        <is>
-          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="B98" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+          <t>Note any selection that makes 5.3 show (Blank), empties the 5.6 line or blanks the last column of 5.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>Checked by: your name or initials.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="inlineStr">
-        <is>
-          <t>Date checked: today’s date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B101" s="14" t="inlineStr">
-        <is>
-          <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Situation</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>Write this in Observed value / evidence</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="n"/>
-      <c r="E102" s="7" t="n"/>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>If you see</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>It means</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="n"/>
+    </row>
+    <row r="101" ht="56.5" customHeight="1">
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Parts 1 and 3 return no unexplained rows, and no selection blanks a visual in Part 2 or Part 3</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>The baseline holds for every choice a reader can make</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="n"/>
+    </row>
+    <row r="102" ht="56.5" customHeight="1">
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Part 1 or Part 3 lists an unexplained combination, or a selection blanks a visual</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Those selections have no 2019 history</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Fail — list them</t>
+        </is>
+      </c>
       <c r="F102" s="8" t="n"/>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>Example of a pass</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>Model: 0 blank combinations · R1 P3: all BeverageClass and ItemType selections tested, 3.2 and 3.10 hold values</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="n"/>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="8" t="n"/>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>Example of another result</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>Non-Alcohol × Unclassified has no 2019 rows — card shows (Blank)</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="8" t="n"/>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="B105" s="20" t="inlineStr">
-        <is>
-          <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
+    <row r="103" ht="29.5" customHeight="1">
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>Remember.  Part 2 is only possible once report R1 is built, and the page steps of Part 3 once R2 Page 2 is built. At the model pass, record Parts 1 and 3’s queries; at the R1 and R2 report passes, update the same row with Part 2 and Part 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="8" customHeight="1"/>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>6.2 In document 26</t>
+          <t>6.1 In document 22</t>
         </is>
       </c>
     </row>
@@ -1716,541 +1655,806 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="29" customHeight="1">
+          <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>Ref in doc 26</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>When it applies</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="n"/>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>G4.05</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>When folder 05 Channel closes</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="B111" s="12" t="inlineStr">
-        <is>
-          <t>G5.07</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>The model pass</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
+          <t>Select the Run Summary tab. Find the row for this run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="29" customHeight="1">
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="29" customHeight="1">
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="29" customHeight="1">
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="16" customHeight="1">
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>G7.04</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>R1 Page 3 finished</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>G8.01</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>R1 report pass</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="n"/>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="8" t="n"/>
-    </row>
-    <row r="114" ht="8" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>7. IF IT FAILS</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>7.1 What usually causes it</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>What you see</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Likely cause</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>What to do</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="n"/>
-    </row>
-    <row r="118" ht="42" customHeight="1">
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>A combination has no 2019 rows</t>
-        </is>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
-        <is>
-          <t>That item type or class did not trade in 2019</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>Decide how to show it: exclude it from the page’s slicer, or label the card; record the decision</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t>Every combination is blank</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>The measure’s 2019 filter does not match DimDate[Year]</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>Check the measure definition in document 02 §8.8</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="B120" s="13" t="inlineStr">
-        <is>
-          <t>7.2 Record the failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="29" customHeight="1">
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t>git -C X:\retail-sector-health log -1 --format=%h</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="6" customHeight="1"/>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>Fill in four cells on that row:</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Checked by: your name or initials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Date checked: today’s date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>On the Check Results tab of document 22, set Result to Fail for check 9. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B122" s="14" t="inlineStr">
-        <is>
-          <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="B123" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C123" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="B124" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C124" s="14" t="inlineStr">
-        <is>
-          <t>Run ID and Check #: this run and check number.</t>
-        </is>
-      </c>
+          <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Situation</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>Write this in Observed value / evidence</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="8" t="n"/>
+    </row>
+    <row r="123" ht="29.5" customHeight="1">
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Example of a pass</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Model: 0 blank combinations · R1 P3: date ranges without 2019 and every 3.6 class tested, 3.2 and 3.10 hold values · R2 P2: every ItemType and BeverageClass selection, 5.3, 5.6, 5.8 hold values</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="n"/>
+      <c r="E123" s="7" t="n"/>
+      <c r="F123" s="8" t="n"/>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>Example of another result</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>Non-Alcohol × Unclassified has no 2019 rows — card shows (Blank)</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="n"/>
+      <c r="E124" s="7" t="n"/>
+      <c r="F124" s="8" t="n"/>
     </row>
     <row r="125" ht="16" customHeight="1">
-      <c r="B125" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C125" s="14" t="inlineStr">
-        <is>
-          <t>What was observed: the same numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="B126" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C126" s="14" t="inlineStr">
-        <is>
-          <t>Root cause: what you found, or ‘not yet known’.</t>
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>6.2 In document 26</t>
         </is>
       </c>
     </row>
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
+          <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="29" customHeight="1">
       <c r="A128" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Ref in doc 26</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>When it applies</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="n"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>G4.05</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>When folder 05 Channel closes</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="n"/>
+      <c r="E130" s="7" t="n"/>
+      <c r="F130" s="8" t="n"/>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>G5.07</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>The model pass</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>G7.04</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>R1 Page 3 finished</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="n"/>
+      <c r="E132" s="7" t="n"/>
+      <c r="F132" s="8" t="n"/>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>G8.01</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>R1 report pass</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="n"/>
+      <c r="E133" s="7" t="n"/>
+      <c r="F133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>G7.07</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>R2 Page 2 finished</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="n"/>
+      <c r="E134" s="7" t="n"/>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>G8.03</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>R2 report pass</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="n"/>
+      <c r="E135" s="7" t="n"/>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="8" customHeight="1"/>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>7. IF IT FAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>7.1 What usually causes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>What you see</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Likely cause</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="n"/>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>A combination has no 2019 rows</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>That item type or class did not trade in 2019</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="n"/>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>Decide how to show it: exclude it from the page’s slicer, or label the card; record the decision</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n"/>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Every combination is blank</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>The measure’s 2019 filter does not match DimDate[Year]</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Check the measure definition in document 02 §8.8</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="n"/>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>7.2 Record the failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="29" customHeight="1">
+      <c r="A143" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>On the Check Results tab of document 22, set Result to Fail for check 9. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>Select the Failure Log tab and fill the first empty row:</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="B146" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Run ID and Check #: this run and check number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="B147" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>Root cause: what you found, or ‘not yet known’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="29" customHeight="1">
+      <c r="A150" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B128" s="14" t="inlineStr">
+      <c r="B150" s="14" t="inlineStr">
         <is>
           <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="16" t="n">
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B129" s="14" t="inlineStr">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="8" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="152" ht="8" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="15" t="inlineStr">
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B132" s="14" t="inlineStr">
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>At the model pass.</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="15" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr">
-        <is>
-          <t>At the R1 report pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="15" t="inlineStr">
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>At the R1 and R2 report passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B134" s="14" t="inlineStr">
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t>After every reload of the county data.</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="8" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
+    <row r="157" ht="8" customHeight="1"/>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="15" t="inlineStr">
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B137" s="14" t="inlineStr">
+      <c r="B159" s="14" t="inlineStr">
         <is>
           <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="15" t="inlineStr">
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B138" s="14" t="inlineStr">
+      <c r="B160" s="14" t="inlineStr">
         <is>
           <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B161" s="14" t="inlineStr">
         <is>
           <t>Document 25 — when each check is run, and when to re-run it.</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="15" t="inlineStr">
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B140" s="14" t="inlineStr">
+      <c r="B162" s="14" t="inlineStr">
         <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="B141" s="21" t="inlineStr">
+    <row r="163" ht="18" customHeight="1">
+      <c r="B163" s="21" t="inlineStr">
         <is>
           <t>Work with DAX query view</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="8" customHeight="1"/>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="164" ht="8" customHeight="1"/>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="29" customHeight="1">
-      <c r="B144" s="14" t="inlineStr">
+    <row r="166" ht="29" customHeight="1">
+      <c r="B166" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="43.5" customHeight="1">
-      <c r="B145" s="14" t="inlineStr">
+    <row r="167" ht="43.5" customHeight="1">
+      <c r="B167" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="139">
+  <mergeCells count="161">
     <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C132:F132"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C122:F122"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C145:F145"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="C110:F110"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B166:F166"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C73:F73"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B108:F108"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="C134:F134"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="E101:F101"/>
     <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="E100:F100"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B160:F160"/>
+    <mergeCell ref="C120:F120"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="E102:F102"/>
     <mergeCell ref="B144:F144"/>
-    <mergeCell ref="E117:F117"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="C135:F135"/>
     <mergeCell ref="B121:F121"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="B56:F56"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C111:F111"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="C111:F111"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="B167:F167"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="B107:F107"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B88:F88"/>
-    <mergeCell ref="C98:F98"/>
-    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C147:F147"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="C146:F146"/>
     <mergeCell ref="C124:F124"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="C148:F148"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="C123:F123"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="C119:F119"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="B75:F75"/>
-    <mergeCell ref="C110:F110"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="C91:F91"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="B161:F161"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B145:F145"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="B87:F87"/>
-    <mergeCell ref="C97:F97"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="C113:F113"/>
-    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="B128:F128"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="C100:F100"/>
     <mergeCell ref="C112:F112"/>
-    <mergeCell ref="B137:F137"/>
     <mergeCell ref="C109:F109"/>
-    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="C133:F133"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="C129:F129"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="E81:F81"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="C140:D140"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B138:F138"/>
-    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B113:F113"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B156:F156"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B155:F155"/>
     <mergeCell ref="B93:F93"/>
-    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="C131:F131"/>
+    <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
-    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="B151:F151"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="C104:F104"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C103:F103"/>
     <mergeCell ref="B127:F127"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C117:F117"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C118:F118"/>
     <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B89:F89"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="C130:F130"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <hyperlinks>
